--- a/paper/RQ3/outputs/260316_collaboration_metrics.xlsx
+++ b/paper/RQ3/outputs/260316_collaboration_metrics.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55,7 +55,7 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0.6723479476202487</v>
+        <v>0.6723779165219536</v>
       </c>
     </row>
     <row r="3">
@@ -74,7 +74,7 @@
         <v>7</v>
       </c>
       <c r="E3">
-        <v>5.9974833125375774e-40</v>
+        <v>1.1025930311677122e-38</v>
       </c>
     </row>
     <row r="4">
@@ -93,7 +93,7 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <v>0.5469422015705898</v>
+        <v>0.5469168170173958</v>
       </c>
     </row>
     <row r="5">
@@ -112,7 +112,7 @@
         <v>12</v>
       </c>
       <c r="E5">
-        <v>0.026622433448152752</v>
+        <v>0.026622797696071513</v>
       </c>
     </row>
     <row r="6">
@@ -131,7 +131,7 @@
         <v>5</v>
       </c>
       <c r="E6">
-        <v>5.4151952581585055e-36</v>
+        <v>7.360049224976659e-35</v>
       </c>
     </row>
     <row r="7">
@@ -150,7 +150,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>0.12377562181948341</v>
+        <v>0.12377526120179971</v>
       </c>
     </row>
     <row r="8">
@@ -169,7 +169,7 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>0.12429230247203926</v>
+        <v>0.12429192052004759</v>
       </c>
     </row>
     <row r="9">
@@ -188,7 +188,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>5.4151952581585055e-36</v>
+        <v>7.360049224976659e-35</v>
       </c>
     </row>
     <row r="10">
@@ -207,7 +207,7 @@
         <v>11</v>
       </c>
       <c r="E10">
-        <v>0.02648861694952283</v>
+        <v>0.026488975220906142</v>
       </c>
     </row>
     <row r="11">
@@ -226,7 +226,7 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>0.13318631648293341</v>
+        <v>0.13318136871554836</v>
       </c>
     </row>
     <row r="12">
@@ -245,7 +245,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>5.4151952581585055e-36</v>
+        <v>7.360049224976659e-35</v>
       </c>
     </row>
     <row r="13">
@@ -264,7 +264,7 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>0.07790462267430612</v>
+        <v>0.07790237529017946</v>
       </c>
     </row>
     <row r="14">
@@ -283,7 +283,7 @@
         <v>5</v>
       </c>
       <c r="E14">
-        <v>0.017054781310289608</v>
+        <v>0.017055022986349665</v>
       </c>
     </row>
     <row r="15">
@@ -302,7 +302,7 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>0.07491539025525926</v>
+        <v>0.07491324007208282</v>
       </c>
     </row>
     <row r="16">
@@ -321,7 +321,7 @@
         <v>5</v>
       </c>
       <c r="E16">
-        <v>5.4151952581585055e-36</v>
+        <v>7.360049224976659e-35</v>
       </c>
     </row>
     <row r="17">
@@ -340,7 +340,7 @@
         <v>5</v>
       </c>
       <c r="E17">
-        <v>5.4151952581585055e-36</v>
+        <v>7.360049224976659e-35</v>
       </c>
     </row>
     <row r="18">
@@ -359,7 +359,7 @@
         <v>5</v>
       </c>
       <c r="E18">
-        <v>5.4151952581585055e-36</v>
+        <v>7.360049224976659e-35</v>
       </c>
     </row>
     <row r="19">
@@ -378,7 +378,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>0.16616038700654656</v>
+        <v>0.16615641859990354</v>
       </c>
     </row>
     <row r="20">
@@ -397,7 +397,7 @@
         <v>4</v>
       </c>
       <c r="E20">
-        <v>6.574957108345493e-45</v>
+        <v>1.745378256178252e-43</v>
       </c>
     </row>
     <row r="21">
@@ -416,7 +416,7 @@
         <v>4</v>
       </c>
       <c r="E21">
-        <v>0.05194128232641132</v>
+        <v>0.051943500597592264</v>
       </c>
     </row>
     <row r="22">
@@ -435,7 +435,7 @@
         <v>6</v>
       </c>
       <c r="E22">
-        <v>0.1525899191730247</v>
+        <v>0.15258555508318455</v>
       </c>
     </row>
     <row r="23">
@@ -454,7 +454,7 @@
         <v>4</v>
       </c>
       <c r="E23">
-        <v>6.574957108345493e-45</v>
+        <v>1.745378256178252e-43</v>
       </c>
     </row>
     <row r="24">
@@ -473,7 +473,7 @@
         <v>8</v>
       </c>
       <c r="E24">
-        <v>0.22522073761056016</v>
+        <v>0.22521383476965595</v>
       </c>
     </row>
     <row r="25">
@@ -492,7 +492,7 @@
         <v>4</v>
       </c>
       <c r="E25">
-        <v>6.574957108345493e-45</v>
+        <v>1.745378256178252e-43</v>
       </c>
     </row>
     <row r="26">
@@ -511,7 +511,7 @@
         <v>4</v>
       </c>
       <c r="E26">
-        <v>6.574957108345493e-45</v>
+        <v>1.745378256178252e-43</v>
       </c>
     </row>
     <row r="27">
@@ -530,7 +530,7 @@
         <v>4</v>
       </c>
       <c r="E27">
-        <v>6.574957108345493e-45</v>
+        <v>1.745378256178252e-43</v>
       </c>
     </row>
     <row r="28">
@@ -549,7 +549,7 @@
         <v>4</v>
       </c>
       <c r="E28">
-        <v>0.12297351391988402</v>
+        <v>0.12297315673812106</v>
       </c>
     </row>
     <row r="29">
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E29">
-        <v>4.6509005269347845e-40</v>
+        <v>8.550337270522257e-39</v>
       </c>
     </row>
     <row r="30">
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="E30">
-        <v>0.05194128232641132</v>
+        <v>0.051943500597592264</v>
       </c>
     </row>
     <row r="31">
@@ -606,7 +606,7 @@
         <v>4</v>
       </c>
       <c r="E31">
-        <v>1.6723656533443597e-64</v>
+        <v>3.1569328282070173e-62</v>
       </c>
     </row>
     <row r="32">
@@ -625,7 +625,7 @@
         <v>3</v>
       </c>
       <c r="E32">
-        <v>0.07680256486050585</v>
+        <v>0.07680035665993232</v>
       </c>
     </row>
     <row r="33">
@@ -644,7 +644,7 @@
         <v>3</v>
       </c>
       <c r="E33">
-        <v>2.8728180194212856e-69</v>
+        <v>4.775882129061613e-67</v>
       </c>
     </row>
     <row r="34">
@@ -663,7 +663,7 @@
         <v>4</v>
       </c>
       <c r="E34">
-        <v>0.12510306900516208</v>
+        <v>0.1250978924966996</v>
       </c>
     </row>
     <row r="35">
@@ -682,7 +682,7 @@
         <v>3</v>
       </c>
       <c r="E35">
-        <v>2.37892157689121e-40</v>
+        <v>4.373471697522656e-39</v>
       </c>
     </row>
     <row r="36">
@@ -701,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="E36">
-        <v>2.37892157689121e-40</v>
+        <v>4.373471697522656e-39</v>
       </c>
     </row>
     <row r="37">
@@ -720,7 +720,7 @@
         <v>5</v>
       </c>
       <c r="E37">
-        <v>7.000480280659237e-40</v>
+        <v>1.2869866192284633e-38</v>
       </c>
     </row>
     <row r="38">
@@ -739,7 +739,7 @@
         <v>3</v>
       </c>
       <c r="E38">
-        <v>2.37892157689121e-40</v>
+        <v>4.373471697522656e-39</v>
       </c>
     </row>
     <row r="39">
@@ -758,7 +758,7 @@
         <v>3</v>
       </c>
       <c r="E39">
-        <v>0.004858214345797944</v>
+        <v>0.004858152889494659</v>
       </c>
     </row>
     <row r="40">
@@ -777,7 +777,7 @@
         <v>5</v>
       </c>
       <c r="E40">
-        <v>7.000480280659237e-40</v>
+        <v>1.2869866192284633e-38</v>
       </c>
     </row>
     <row r="41">
@@ -796,7 +796,7 @@
         <v>4</v>
       </c>
       <c r="E41">
-        <v>0.010459360527248461</v>
+        <v>0.01045901274826986</v>
       </c>
     </row>
     <row r="42">
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="E42">
-        <v>0.07311112214259978</v>
+        <v>0.07310901721660898</v>
       </c>
     </row>
     <row r="43">
@@ -834,7 +834,7 @@
         <v>4</v>
       </c>
       <c r="E43">
-        <v>0.010459360527248461</v>
+        <v>0.01045901274826986</v>
       </c>
     </row>
     <row r="44">
@@ -853,7 +853,7 @@
         <v>3</v>
       </c>
       <c r="E44">
-        <v>0.002265883487539029</v>
+        <v>0.0022658490809213763</v>
       </c>
     </row>
     <row r="45">
@@ -872,7 +872,7 @@
         <v>3</v>
       </c>
       <c r="E45">
-        <v>0.004858214345797944</v>
+        <v>0.004858152889494659</v>
       </c>
     </row>
     <row r="46">
@@ -891,7 +891,7 @@
         <v>3</v>
       </c>
       <c r="E46">
-        <v>4.1466524194273977e-60</v>
+        <v>3.454680828043473e-58</v>
       </c>
     </row>
     <row r="47">
@@ -910,7 +910,7 @@
         <v>2</v>
       </c>
       <c r="E47">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="48">
@@ -929,7 +929,7 @@
         <v>2</v>
       </c>
       <c r="E48">
-        <v>0.007125903962116736</v>
+        <v>0.007126095115026903</v>
       </c>
     </row>
     <row r="49">
@@ -948,7 +948,7 @@
         <v>2</v>
       </c>
       <c r="E49">
-        <v>0.03279922489054862</v>
+        <v>0.03280023551303591</v>
       </c>
     </row>
     <row r="50">
@@ -967,7 +967,7 @@
         <v>2</v>
       </c>
       <c r="E50">
-        <v>2.455218526371594e-69</v>
+        <v>4.0816488213900796e-67</v>
       </c>
     </row>
     <row r="51">
@@ -986,7 +986,7 @@
         <v>2</v>
       </c>
       <c r="E51">
-        <v>2.455218526371594e-69</v>
+        <v>4.0816488213900796e-67</v>
       </c>
     </row>
     <row r="52">
@@ -1005,7 +1005,7 @@
         <v>2</v>
       </c>
       <c r="E52">
-        <v>0.000207261746455041</v>
+        <v>0.0002072646729092354</v>
       </c>
     </row>
     <row r="53">
@@ -1024,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="E53">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="54">
@@ -1043,7 +1043,7 @@
         <v>2</v>
       </c>
       <c r="E54">
-        <v>3.0355602523492655e-60</v>
+        <v>2.5290018900619425e-58</v>
       </c>
     </row>
     <row r="55">
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="E55">
-        <v>0.18020826949029017</v>
+        <v>0.18020037133639896</v>
       </c>
     </row>
     <row r="56">
@@ -1081,7 +1081,7 @@
         <v>6</v>
       </c>
       <c r="E56">
-        <v>0.013353216110772666</v>
+        <v>0.013353014602590285</v>
       </c>
     </row>
     <row r="57">
@@ -1100,7 +1100,7 @@
         <v>2</v>
       </c>
       <c r="E57">
-        <v>1.886920150820061e-86</v>
+        <v>1.6028767813949925e-83</v>
       </c>
     </row>
     <row r="58">
@@ -1119,7 +1119,7 @@
         <v>2</v>
       </c>
       <c r="E58">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="59">
@@ -1138,7 +1138,7 @@
         <v>2</v>
       </c>
       <c r="E59">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="60">
@@ -1157,7 +1157,7 @@
         <v>2</v>
       </c>
       <c r="E60">
-        <v>0.0014394185922724184</v>
+        <v>0.0014393959288825913</v>
       </c>
     </row>
     <row r="61">
@@ -1176,7 +1176,7 @@
         <v>3</v>
       </c>
       <c r="E61">
-        <v>4.1466524194273977e-60</v>
+        <v>3.454680828043473e-58</v>
       </c>
     </row>
     <row r="62">
@@ -1195,7 +1195,7 @@
         <v>2</v>
       </c>
       <c r="E62">
-        <v>0.000207261746455041</v>
+        <v>0.0002072646729092354</v>
       </c>
     </row>
     <row r="63">
@@ -1214,7 +1214,7 @@
         <v>2</v>
       </c>
       <c r="E63">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="64">
@@ -1233,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="E64">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="65">
@@ -1252,7 +1252,7 @@
         <v>2</v>
       </c>
       <c r="E65">
-        <v>0.007125903962116736</v>
+        <v>0.007126095115026903</v>
       </c>
     </row>
     <row r="66">
@@ -1271,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="67">
@@ -1290,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="68">
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="E68">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="69">
@@ -1328,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="E69">
-        <v>1.323826509738712e-69</v>
+        <v>2.2007796272152104e-67</v>
       </c>
     </row>
     <row r="70">
@@ -1347,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="E70">
-        <v>0.0014293089287752765</v>
+        <v>0.0014292864612480251</v>
       </c>
     </row>
     <row r="71">
@@ -1366,7 +1366,7 @@
         <v>1</v>
       </c>
       <c r="E71">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="72">
@@ -1385,7 +1385,7 @@
         <v>1</v>
       </c>
       <c r="E72">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="73">
@@ -1404,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>0.01278760544195237</v>
+        <v>0.012788011140424632</v>
       </c>
     </row>
     <row r="74">
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="75">
@@ -1442,7 +1442,7 @@
         <v>2</v>
       </c>
       <c r="E75">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="76">
@@ -1461,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <v>1.0287114621900934e-40</v>
+        <v>1.8912100796045982e-39</v>
       </c>
     </row>
     <row r="77">
@@ -1480,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="78">
@@ -1499,7 +1499,7 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>0.00627818908806134</v>
+        <v>0.006278388975343642</v>
       </c>
     </row>
     <row r="79">
@@ -1518,7 +1518,7 @@
         <v>1</v>
       </c>
       <c r="E79">
-        <v>1.886920150820061e-86</v>
+        <v>8.014383906974963e-84</v>
       </c>
     </row>
     <row r="80">
@@ -1537,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="81">
@@ -1556,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>0.00012063004011717024</v>
+        <v>0.00012063214695605249</v>
       </c>
     </row>
     <row r="82">
@@ -1575,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="E82">
-        <v>0.05634894785677043</v>
+        <v>0.05634616181887394</v>
       </c>
     </row>
     <row r="83">
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="E83">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="84">
@@ -1613,7 +1613,7 @@
         <v>1</v>
       </c>
       <c r="E84">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="85">
@@ -1632,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="E85">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="86">
@@ -1651,7 +1651,7 @@
         <v>2</v>
       </c>
       <c r="E86">
-        <v>2.2298208711258123e-64</v>
+        <v>1.5784664141035089e-62</v>
       </c>
     </row>
     <row r="87">
@@ -1670,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="E87">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="88">
@@ -1689,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="E88">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="89">
@@ -1708,7 +1708,7 @@
         <v>1</v>
       </c>
       <c r="E89">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="90">
@@ -1727,7 +1727,7 @@
         <v>2</v>
       </c>
       <c r="E90">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="91">
@@ -1746,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>0.01278760544195237</v>
+        <v>0.012788011140424632</v>
       </c>
     </row>
     <row r="92">
@@ -1765,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="E92">
-        <v>0.010373097291625558</v>
+        <v>0.010373130812997594</v>
       </c>
     </row>
     <row r="93">
@@ -1784,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="E93">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="94">
@@ -1803,7 +1803,7 @@
         <v>1</v>
       </c>
       <c r="E94">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="95">
@@ -1822,7 +1822,7 @@
         <v>1</v>
       </c>
       <c r="E95">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="96">
@@ -1841,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="E96">
-        <v>1.3265559631238551e-40</v>
+        <v>2.4387752064881975e-39</v>
       </c>
     </row>
     <row r="97">
@@ -1860,7 +1860,7 @@
         <v>1</v>
       </c>
       <c r="E97">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="98">
@@ -1879,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="E98">
-        <v>0.0014293089287752765</v>
+        <v>0.0014292864612480251</v>
       </c>
     </row>
     <row r="99">
@@ -1898,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="E99">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="100">
@@ -1917,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="E100">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="101">
@@ -1936,7 +1936,7 @@
         <v>2</v>
       </c>
       <c r="E101">
-        <v>1.3278020137673604e-72</v>
+        <v>2.8198106544575423e-70</v>
       </c>
     </row>
     <row r="102">
@@ -1955,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="E102">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="103">
@@ -1974,7 +1974,7 @@
         <v>1</v>
       </c>
       <c r="E103">
-        <v>1.886920150820061e-86</v>
+        <v>8.014383906974963e-84</v>
       </c>
     </row>
     <row r="104">
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="E104">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="105">
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="E105">
-        <v>1.1149104355629062e-64</v>
+        <v>7.892332070517544e-63</v>
       </c>
     </row>
     <row r="106">
@@ -2031,7 +2031,7 @@
         <v>1</v>
       </c>
       <c r="E106">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="107">
@@ -2050,7 +2050,7 @@
         <v>1</v>
       </c>
       <c r="E107">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="108">
@@ -2069,7 +2069,7 @@
         <v>1</v>
       </c>
       <c r="E108">
-        <v>0.0111614259199789</v>
+        <v>0.01116188587977714</v>
       </c>
     </row>
     <row r="109">
@@ -2088,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="E109">
-        <v>2.681474812249094e-100</v>
+        <v>4.555649813354968e-97</v>
       </c>
     </row>
     <row r="110">
@@ -2107,7 +2107,729 @@
         <v>1</v>
       </c>
       <c r="E110">
-        <v>1.1149104355629062e-64</v>
+        <v>7.892332070517544e-63</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Alan Reiner</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Alex Morcos</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Andy Chase</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>1</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Chris Priest</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Chris Stewart</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Christopher Gilliard</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Craig Raw</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>2</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Daniel Weigl</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Dathon Ohm</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Dmitry Petukhov</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Fabian Jahr</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>1</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Fontaine</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+      <c r="E122">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Gloria Zhao</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123">
+        <v>0</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Gregory Sanders</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>James Hilliard</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+      <c r="E125">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>John Carvalho</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+      <c r="E126">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jorge Timón</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>1</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+      <c r="E127">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Kalle Rosenbaum</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>2</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+      <c r="E128">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Kristov Atlas</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+      <c r="E129">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Marco Pontello</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+      <c r="E130">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Maxim Orlovsky</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>1</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+      <c r="E131">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Murch</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>1</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+      <c r="E132">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>OceanSlim</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+      <c r="E133">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Oren Z</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+      <c r="E134">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Robert Spigler</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>1</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+      <c r="E135">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Ryan Havar</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>1</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+      <c r="E136">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Salvatore Ingala</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>2</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+      <c r="E137">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Sancho Panza</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+      <c r="E138">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Stefan Thomas</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>1</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+      <c r="E139">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Stephen Pair</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+      <c r="E140">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Suhas Daftuar</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+      <c r="E141">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Toby Padilla</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+      <c r="E142">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Tom Briar</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+      <c r="E143">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Tom Zander</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>1</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+      <c r="E144">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Upal Chakraborty</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>1</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+      <c r="E145">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Washington Y. Sanchez</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+      <c r="E146">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Wladimir J. van der Laan</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>1</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+      <c r="E147">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>t.khan</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+      <c r="E148">
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
